--- a/research/traditional_assets/database/data/vietnam/vietnam_entertainment.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_entertainment.xlsx
@@ -587,26 +587,8 @@
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.247</v>
-      </c>
-      <c r="G2">
-        <v>-0.1811428571428571</v>
-      </c>
-      <c r="H2">
-        <v>-0.1811428571428571</v>
-      </c>
-      <c r="I2">
-        <v>-0.1825691938050401</v>
-      </c>
-      <c r="J2">
-        <v>-0.1825691938050401</v>
-      </c>
       <c r="K2">
-        <v>-7.82</v>
-      </c>
-      <c r="L2">
-        <v>-0.1489523809523809</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -614,18 +596,12 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2">
-        <v>-0</v>
-      </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>-0</v>
-      </c>
       <c r="S2">
         <v>0</v>
       </c>
@@ -636,61 +612,55 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.107840700488697</v>
+        <v>0.1978656569133055</v>
       </c>
       <c r="Z2">
-        <v>11.11249076782553</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-2.028798480647859</v>
+        <v>0.1603978947405817</v>
       </c>
       <c r="AB2">
-        <v>0.1006080804446276</v>
+        <v>0.164267373280491</v>
       </c>
       <c r="AC2">
-        <v>-2.129406561092486</v>
+        <v>-0.003869478539909238</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>4.72441337382304</v>
+        <v>4.328549147388624</v>
       </c>
       <c r="AF2">
-        <v>4.72441337382304</v>
+        <v>4.328549147388624</v>
       </c>
       <c r="AG2">
-        <v>4.72441337382304</v>
+        <v>4.328549147388624</v>
       </c>
       <c r="AH2">
-        <v>0.1186310851455866</v>
+        <v>0.270052461241873</v>
       </c>
       <c r="AI2">
         <v>1</v>
       </c>
       <c r="AJ2">
-        <v>0.1186310851455866</v>
+        <v>0.270052461241873</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AL2">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
-      </c>
-      <c r="AO2">
-        <v>-67.10526315789474</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.5942658331852881</v>
-      </c>
-      <c r="AQ2">
-        <v>92.72727272727271</v>
+        <v>2.774710991915784</v>
       </c>
     </row>
     <row r="3">
@@ -709,26 +679,8 @@
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.247</v>
-      </c>
-      <c r="G3">
-        <v>-0.1811428571428571</v>
-      </c>
-      <c r="H3">
-        <v>-0.1811428571428571</v>
-      </c>
-      <c r="I3">
-        <v>-0.1825691938050401</v>
-      </c>
-      <c r="J3">
-        <v>-0.1825691938050401</v>
-      </c>
       <c r="K3">
-        <v>-7.82</v>
-      </c>
-      <c r="L3">
-        <v>-0.1489523809523809</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -736,18 +688,12 @@
       <c r="N3">
         <v>-0</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
         <v>0</v>
       </c>
@@ -758,61 +704,55 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.107840700488697</v>
+        <v>0.1978656569133055</v>
       </c>
       <c r="Z3">
-        <v>11.11249076782553</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-2.028798480647859</v>
+        <v>0.1603978947405817</v>
       </c>
       <c r="AB3">
-        <v>0.1006080804446276</v>
+        <v>0.164267373280491</v>
       </c>
       <c r="AC3">
-        <v>-2.129406561092486</v>
+        <v>-0.003869478539909238</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>4.72441337382304</v>
+        <v>4.328549147388624</v>
       </c>
       <c r="AF3">
-        <v>4.72441337382304</v>
+        <v>4.328549147388624</v>
       </c>
       <c r="AG3">
-        <v>4.72441337382304</v>
+        <v>4.328549147388624</v>
       </c>
       <c r="AH3">
-        <v>0.1186310851455866</v>
+        <v>0.270052461241873</v>
       </c>
       <c r="AI3">
         <v>1</v>
       </c>
       <c r="AJ3">
-        <v>0.1186310851455866</v>
+        <v>0.270052461241873</v>
       </c>
       <c r="AK3">
         <v>1</v>
       </c>
       <c r="AL3">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AO3">
-        <v>-67.10526315789474</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.5942658331852881</v>
-      </c>
-      <c r="AQ3">
-        <v>92.72727272727271</v>
+        <v>2.774710991915784</v>
       </c>
     </row>
   </sheetData>
